--- a/jogos_2025-02-26.xlsx
+++ b/jogos_2025-02-26.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -658,7 +658,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="M2" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="N2" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="O2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X2" t="n">
         <v>2.95</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="Y2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA2" t="n">
         <v>3.6</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AB2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['66', '74']</t>
+          <t>['10', '78']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45714.29166666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.59</v>
+        <v>1.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3.98</v>
       </c>
       <c r="N3" t="n">
-        <v>2.81</v>
+        <v>4.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['31', '59', '90+6']</t>
+          <t>['90+11']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45714.29166666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="M4" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>3.97</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45714.29166666666</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>2.59</v>
       </c>
       <c r="M6" t="n">
-        <v>3.98</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>2.81</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['31', '59', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.42</v>
       </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['90+11']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45714.29166666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>3.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.12</v>
+        <v>3.78</v>
       </c>
       <c r="N8" t="n">
-        <v>3.97</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45714.29166666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="N9" t="n">
-        <v>3.69</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
         <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.83</v>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['10', '78']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>1.66</v>
       </c>
-      <c r="AI9" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45714.29166666666</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1690,10 +1690,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="N10" t="n">
-        <v>2.61</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.03</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['66', '74']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.88</v>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['26', '49']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45714.29166666666</v>
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.78</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>2.61</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X11" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.6</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['26', '49']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45714.29166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Inđija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Sloven Ruma</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
         <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="T16" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U16" t="n">
         <v>1.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['58', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45714.41666666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>3.68</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45714.41666666666</v>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="O18" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
-        <v>4.5</v>
+        <v>2.91</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.38</v>
+        <v>3.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['3', '6', '60']</t>
+          <t>['22', '39', '72', '74', '77']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45714.41666666666</v>
@@ -2826,32 +2826,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kedah</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" t="n">
         <v>2.3</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.38</v>
+        <v>5.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['40', '86']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI19" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45714.41666666666</v>
@@ -2955,35 +2955,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kedah</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X20" t="n">
         <v>4.5</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.77</v>
-      </c>
       <c r="Y20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA20" t="n">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['40', '86']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.74</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45714.41666666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="R21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.53</v>
       </c>
-      <c r="O21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.37</v>
-      </c>
       <c r="X21" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['58', '64']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['22', '39', '72', '74', '77']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="AI21" t="n">
-        <v>3.75</v>
+        <v>1.53</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>3.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45714.41666666666</v>
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O22" t="n">
         <v>2.75</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="S22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.26</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['14', '30', '48']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45714.41666666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,28 +3378,28 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.1</v>
       </c>
       <c r="T23" t="n">
         <v>4.1</v>
@@ -3408,53 +3408,53 @@
         <v>1.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.7</v>
+        <v>6.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
         <v>2.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['40', '50', '72', '90+3']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG23" t="n">
         <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45714.41666666666</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inđija</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sloven Ruma</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.7</v>
+        <v>2.38</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3570,20 +3570,20 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '6', '60']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.57</v>
+        <v>1.03</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.73</v>
+        <v>4.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.63</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45714.41666666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.3</v>
       </c>
-      <c r="M25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.1</v>
       </c>
-      <c r="Y25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['40', '50', '72', '90+3']</t>
+          <t>['14', '30', '48']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45714.41666666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Enyimba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9.5</v>
+        <v>1.61</v>
       </c>
       <c r="M26" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="N26" t="n">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.7</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.06</v>
+        <v>2.06</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.6</v>
+        <v>1.44</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>4.33</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45714.45833333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Enyimba</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.61</v>
+        <v>9.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>1.37</v>
       </c>
       <c r="O29" t="n">
+        <v>8</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.3</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="U29" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.06</v>
+        <v>1.06</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.44</v>
+        <v>4.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45714.45833333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Abia Warriors</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="M32" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="R32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.47</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X32" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4602,20 +4602,20 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['45+3', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45714.5</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heartland</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.52</v>
+        <v>10</v>
       </c>
       <c r="M33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['18', '45+3', '90+7']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>3.6</v>
       </c>
-      <c r="N33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="AH33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.25</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45714.5</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,28 +4797,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
-        <v>3.23</v>
+        <v>3.51</v>
       </c>
       <c r="N34" t="n">
-        <v>3.38</v>
+        <v>5.4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="P34" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T34" t="n">
         <v>3.42</v>
@@ -4830,50 +4830,50 @@
         <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="X34" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="Z34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '68']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45714.5</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,65 +4926,65 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>8.800000000000001</v>
+        <v>6.24</v>
       </c>
       <c r="O35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="X35" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45714.5</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,65 +5055,65 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="N36" t="n">
-        <v>6.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="X36" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45714.5</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,109 +5158,109 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Heartland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P37" t="n">
         <v>2</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>10</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="O37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P37" t="n">
-        <v>3.05</v>
-      </c>
       <c r="Q37" t="n">
+        <v>8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.5</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['18', '45+3', '90+7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>3.6</v>
+        <v>1.11</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45714.5</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Abia Warriors</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.54</v>
+        <v>2.16</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>3.38</v>
       </c>
       <c r="O38" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="P38" t="n">
         <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="T38" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="U38" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="V38" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W38" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X38" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AC38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45714.5</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N41" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P41" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
         <v>3.5</v>
       </c>
       <c r="R41" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.57</v>
       </c>
-      <c r="S41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X41" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>5.2</v>
+        <v>6.25</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45714.54166666666</v>
@@ -5803,19 +5803,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="M42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC42" t="n">
         <v>2.9</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD42" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
       <c r="AG42" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.33</v>
+        <v>2.85</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45714.54166666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,65 +5958,65 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="P43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S43" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q43" t="n">
-        <v>9</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T43" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="X43" t="n">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.85</v>
+        <v>1.44</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="AJ43" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45714.54166666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,19 +6835,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="M50" t="n">
-        <v>3.17</v>
+        <v>3.78</v>
       </c>
       <c r="N50" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="O50" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P50" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="R50" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="S50" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V50" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="X50" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['50', '79']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.46</v>
+        <v>2.07</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45714.64583333334</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,109 +6964,109 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X51" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>['50', '79']</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45714.64583333334</v>
@@ -7222,81 +7222,81 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N53" t="n">
         <v>3</v>
       </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N53" t="n">
-        <v>5.75</v>
-      </c>
       <c r="O53" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="P53" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB53" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.47</v>
       </c>
       <c r="AC53" t="n">
         <v>1.8</v>
@@ -7306,25 +7306,25 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['22', '26', '47']</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['4', '45+2']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45714.6875</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,55 +7377,55 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z54" t="n">
         <v>2.2</v>
       </c>
-      <c r="M54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N54" t="n">
-        <v>3</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>4</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X54" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA54" t="n">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AC54" t="n">
         <v>1.8</v>
@@ -7435,25 +7435,25 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['45+4']</t>
+          <t>['22', '26', '47']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['4', '45+2']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45714.6875</v>
@@ -7738,109 +7738,109 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T57" t="n">
         <v>3</v>
       </c>
-      <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U57" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
         <v>1.05</v>
       </c>
       <c r="W57" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X57" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>['56', '63', '90+5']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['18', '90', '90+10']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45714.69791666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,25 +7867,25 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Loughgall</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.49</v>
+        <v>3.9</v>
       </c>
       <c r="M58" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>2.74</v>
+        <v>1.73</v>
       </c>
       <c r="O58" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="P58" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="R58" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
         <v>1.36</v>
       </c>
-      <c r="S58" t="n">
-        <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V58" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X58" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '17', '50', '87']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.8</v>
+        <v>3.02</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45714.69791666666</v>
@@ -7996,22 +7996,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -8022,22 +8022,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="M59" t="n">
-        <v>3.47</v>
+        <v>3.29</v>
       </c>
       <c r="N59" t="n">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="O59" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P59" t="n">
         <v>2.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
         <v>1.36</v>
@@ -8052,13 +8052,13 @@
         <v>1.44</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W59" t="n">
         <v>1.28</v>
       </c>
       <c r="X59" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Y59" t="n">
         <v>1.77</v>
@@ -8067,38 +8067,38 @@
         <v>1.98</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD59" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ59" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>['12', '84']</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45714.69791666666</v>
@@ -8125,109 +8125,109 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N60" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O60" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P60" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U60" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T60" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.36</v>
       </c>
       <c r="V60" t="n">
         <v>1.05</v>
       </c>
       <c r="W60" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X60" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Y60" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z60" t="n">
         <v>1.98</v>
       </c>
-      <c r="Z60" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AA60" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['56', '63', '90+5']</t>
+          <t>['12', '84']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AJ60" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45714.69791666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,25 +8254,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Loughgall</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G61" t="n">
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.9</v>
+        <v>2.56</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="N61" t="n">
-        <v>1.73</v>
+        <v>2.64</v>
       </c>
       <c r="O61" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P61" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>['18', '90', '90+10']</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
         <v>1.47</v>
       </c>
-      <c r="S61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T61" t="n">
-        <v>3</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X61" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>['13', '17', '50', '87']</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH61" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AI61" t="n">
-        <v>3.02</v>
+        <v>2.1</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45714.69791666666</v>
@@ -8770,109 +8770,109 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UCV</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M65" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="N65" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X65" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC65" t="n">
         <v>2</v>
       </c>
-      <c r="I65" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" t="n">
-        <v>2</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
+      <c r="AD65" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>['45+9']</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
         <v>1.05</v>
       </c>
-      <c r="M65" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="N65" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>21</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S65" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X65" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>['3', '40', '89']</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['6', '45+1']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AH65" t="n">
-        <v>7</v>
+        <v>3.24</v>
       </c>
       <c r="AI65" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AJ65" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45714.89583333334</v>
@@ -8899,25 +8899,25 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>UCV</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8925,83 +8925,83 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="M66" t="n">
-        <v>4.87</v>
+        <v>13.05</v>
       </c>
       <c r="N66" t="n">
-        <v>7.75</v>
+        <v>28.5</v>
       </c>
       <c r="O66" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="P66" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q66" t="n">
+        <v>21</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X66" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>['3', '40', '89']</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>['6', '45+1']</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AJ66" t="n">
         <v>7.5</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X66" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>['45+9']</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45714.89583333334</v>
